--- a/ArenaBattle/GaneData/ABCharacterStatTable.xlsx
+++ b/ArenaBattle/GaneData/ABCharacterStatTable.xlsx
@@ -1,26 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26130"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\UE5Part2\PreTest\ArenaBattle10pre\GameData\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B6DBFFE-125E-4A66-AF5B-85CEEB9F49AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="Polaris Office Sheet" lastEdited="7" lowestEdited="7" rupBuild="10.105.293.56114"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="570" yWindow="1120" windowWidth="31540" windowHeight="17940" xr2:uid="{14535CBB-5647-4022-885E-3A0FC95BEC4B}"/>
+    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" tabRatio="590" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Player" sheetId="2" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
@@ -28,27 +18,21 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>Attack</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>MaxHP</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Name</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>AttackSpeed</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>AttackRange</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>CLVL1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>CLVL2</t>
@@ -84,43 +68,598 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="20">
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color theme="10"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color theme="11"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FFFF0000"/>
+    </font>
+    <font>
+      <sz val="18.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color theme="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color theme="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color theme="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color theme="3"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FF3F3F76"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FF3F3F3F"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FFFA7D00"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FFFFFFFF"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FFFA7D00"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color theme="1"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FF006100"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FF9C0006"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FF9C6500"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color theme="0"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FF7F7F7F"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="gray125">
+        <fgColor rgb="FF000000"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599990"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599990"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599990"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599990"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599990"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599990"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color rgb="FFACCCEA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.399980"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="7" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="5" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="0" applyFont="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="7" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="30" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="31" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -132,19 +671,57 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
+    <cellStyle name="20% - 강조색1" xfId="25" builtinId="30"/>
+    <cellStyle name="20% - 강조색2" xfId="29" builtinId="34"/>
+    <cellStyle name="20% - 강조색3" xfId="33" builtinId="38"/>
+    <cellStyle name="20% - 강조색4" xfId="37" builtinId="42"/>
+    <cellStyle name="20% - 강조색5" xfId="41" builtinId="46"/>
+    <cellStyle name="20% - 강조색6" xfId="45" builtinId="50"/>
+    <cellStyle name="40% - 강조색1" xfId="26" builtinId="31"/>
+    <cellStyle name="40% - 강조색2" xfId="30" builtinId="35"/>
+    <cellStyle name="40% - 강조색3" xfId="34" builtinId="39"/>
+    <cellStyle name="40% - 강조색4" xfId="38" builtinId="43"/>
+    <cellStyle name="40% - 강조색5" xfId="42" builtinId="47"/>
+    <cellStyle name="40% - 강조색6" xfId="46" builtinId="51"/>
+    <cellStyle name="60% - 강조색1" xfId="27" builtinId="32"/>
+    <cellStyle name="60% - 강조색2" xfId="31" builtinId="36"/>
+    <cellStyle name="60% - 강조색3" xfId="35" builtinId="40"/>
+    <cellStyle name="60% - 강조색4" xfId="39" builtinId="44"/>
+    <cellStyle name="60% - 강조색5" xfId="43" builtinId="48"/>
+    <cellStyle name="60% - 강조색6" xfId="47" builtinId="52"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="강조색1" xfId="24" builtinId="29"/>
+    <cellStyle name="강조색2" xfId="28" builtinId="33"/>
+    <cellStyle name="강조색3" xfId="32" builtinId="37"/>
+    <cellStyle name="강조색4" xfId="36" builtinId="41"/>
+    <cellStyle name="강조색5" xfId="40" builtinId="45"/>
+    <cellStyle name="강조색6" xfId="44" builtinId="49"/>
+    <cellStyle name="경고문" xfId="9" builtinId="11"/>
+    <cellStyle name="계산" xfId="17" builtinId="22"/>
+    <cellStyle name="나쁨" xfId="22" builtinId="27"/>
+    <cellStyle name="메모" xfId="8" builtinId="10"/>
+    <cellStyle name="백분율" xfId="3" builtinId="5"/>
+    <cellStyle name="보통" xfId="23" builtinId="28"/>
+    <cellStyle name="설명텍스트" xfId="48" builtinId="53"/>
+    <cellStyle name="셀 확인" xfId="18" builtinId="23"/>
+    <cellStyle name="쉼표" xfId="1" builtinId="3"/>
+    <cellStyle name="쉼표[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="연결된 셀" xfId="19" builtinId="24"/>
+    <cellStyle name="열어본 하이퍼링크" xfId="7" builtinId="9" hidden="1"/>
+    <cellStyle name="요약" xfId="20" builtinId="25"/>
+    <cellStyle name="입력" xfId="15" builtinId="20"/>
+    <cellStyle name="제목" xfId="10" builtinId="15"/>
+    <cellStyle name="제목 1" xfId="11" builtinId="16"/>
+    <cellStyle name="제목 2" xfId="12" builtinId="17"/>
+    <cellStyle name="제목 3" xfId="13" builtinId="18"/>
+    <cellStyle name="제목 4" xfId="14" builtinId="19"/>
+    <cellStyle name="좋음" xfId="21" builtinId="26"/>
+    <cellStyle name="출력" xfId="16" builtinId="21"/>
+    <cellStyle name="통화" xfId="2" builtinId="4"/>
+    <cellStyle name="통화[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="하이퍼링크" xfId="6" builtinId="8" hidden="1"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -444,16 +1021,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3D538BA-27C2-42AB-99FE-D911400E397E}">
-  <dimension ref="A2:F12"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr defaultRowHeight="16.500000"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" style="1"/>
-    <col min="4" max="5" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.75" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="1" width="8.88000011" customWidth="1" outlineLevel="0"/>
+    <col min="4" max="5" width="11.63000011" customWidth="1" outlineLevel="0"/>
+    <col min="6" max="6" width="15.75500011" customWidth="1" outlineLevel="0"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -469,11 +1046,11 @@
       <c r="E2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="0" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -481,7 +1058,7 @@
         <v>100</v>
       </c>
       <c r="C3" s="1">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="D3" s="1">
         <v>40</v>
@@ -493,7 +1070,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:6">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -501,7 +1078,7 @@
         <v>150</v>
       </c>
       <c r="C4" s="1">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="D4" s="1">
         <v>40</v>
@@ -513,7 +1090,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:6">
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
@@ -521,19 +1098,19 @@
         <v>200</v>
       </c>
       <c r="C5" s="1">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="D5" s="1">
         <v>40</v>
       </c>
       <c r="E5" s="1">
-        <v>1.1000000000000001</v>
+        <v>1.1</v>
       </c>
       <c r="F5" s="1">
         <v>400</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:6">
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
@@ -547,13 +1124,13 @@
         <v>40</v>
       </c>
       <c r="E6" s="1">
-        <v>1.1499999999999999</v>
+        <v>1.15</v>
       </c>
       <c r="F6" s="1">
         <v>400</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:6">
       <c r="A7" s="1" t="s">
         <v>9</v>
       </c>
@@ -561,7 +1138,7 @@
         <v>300</v>
       </c>
       <c r="C7" s="1">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="D7" s="1">
         <v>40</v>
@@ -573,7 +1150,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:6">
       <c r="A8" s="1" t="s">
         <v>10</v>
       </c>
@@ -581,7 +1158,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="1">
-        <v>200</v>
+        <v>240</v>
       </c>
       <c r="D8" s="1">
         <v>40</v>
@@ -593,7 +1170,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:6">
       <c r="A9" s="1" t="s">
         <v>11</v>
       </c>
@@ -601,7 +1178,7 @@
         <v>400</v>
       </c>
       <c r="C9" s="1">
-        <v>220</v>
+        <v>280</v>
       </c>
       <c r="D9" s="1">
         <v>40</v>
@@ -613,7 +1190,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:6">
       <c r="A10" s="1" t="s">
         <v>12</v>
       </c>
@@ -621,7 +1198,7 @@
         <v>450</v>
       </c>
       <c r="C10" s="1">
-        <v>240</v>
+        <v>320</v>
       </c>
       <c r="D10" s="1">
         <v>40</v>
@@ -633,7 +1210,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:6">
       <c r="A11" s="1" t="s">
         <v>13</v>
       </c>
@@ -641,7 +1218,7 @@
         <v>500</v>
       </c>
       <c r="C11" s="1">
-        <v>260</v>
+        <v>360</v>
       </c>
       <c r="D11" s="1">
         <v>40</v>
@@ -653,7 +1230,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:6">
       <c r="A12" s="1" t="s">
         <v>14</v>
       </c>
@@ -661,7 +1238,7 @@
         <v>550</v>
       </c>
       <c r="C12" s="1">
-        <v>280</v>
+        <v>400</v>
       </c>
       <c r="D12" s="1">
         <v>40</v>
@@ -675,6 +1252,7 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.70" right="0.70" top="0.75" bottom="0.75" header="0.30" footer="0.30"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>